--- a/mlef_pipeline/results/DCR/SQUAMOUS/RWD_DP_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/SQUAMOUS/RWD_DP_PYRAD/rwd-only/results.xlsx
@@ -468,12 +468,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.50 ± 0.16</t>
+          <t>0.54 ± 0.15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.24 ± 0.07</t>
+          <t>0.25 ± 0.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -483,7 +483,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.51 ± 0.50</t>
+          <t>0.55 ± 0.50</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.60 ± 0.32</t>
+          <t>0.62 ± 0.39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.44 ± 0.41</t>
+          <t>0.26 ± 0.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>0.20</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.80</t>
         </is>
       </c>
       <c r="F4" t="n">
